--- a/web/public/forms/orig/o-hyuil-jageop.xlsx
+++ b/web/public/forms/orig/o-hyuil-jageop.xlsx
@@ -640,7 +640,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="31" t="inlineStr">

--- a/web/public/forms/orig/o-hyuil-jageop.xlsx
+++ b/web/public/forms/orig/o-hyuil-jageop.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계획서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-계획서" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'계획서'!$A$1:$H$31</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'예시-계획서'!$A$1:$H$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -166,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -255,9 +253,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -847,10 +842,7 @@
       <c r="H13" s="15" t="inlineStr"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="16">
-        <f>IF(COUNTIF(C9:C13,"■")=0,"","※ 체크한 위험작업 "&amp;COUNTIF(C9:C13,"■")&amp;"건"&amp;IF(((C9="■")+(C10="■")+(C11="■"))&gt;0," (고위험작업 "&amp;((C9="■")+(C10="■")+(C11="■"))&amp;"건)","")&amp;" — 작업내용·안전대책에 작업마다 대책을 적으세요.")</f>
-        <v/>
-      </c>
+      <c r="A14" s="16" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -881,17 +873,11 @@
         </is>
       </c>
       <c r="F16" s="8" t="n"/>
-      <c r="G16" s="19">
-        <f>IF(N(F16)=0,"","("&amp;CHOOSE(WEEKDAY(F16),"일","월","화","수","목","금","토")&amp;")")</f>
-        <v/>
-      </c>
+      <c r="G16" s="19" t="n"/>
       <c r="H16" s="20" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="16">
-        <f>IF(N(F16)=0,"",IF(WEEKDAY(F16,2)&lt;=5,"※ 작업일 "&amp;MONTH(F16)&amp;"/"&amp;DAY(F16)&amp;"("&amp;CHOOSE(WEEKDAY(F16),"일","월","화","수","목","금","토")&amp;")은 평일입니다 — 공휴일 작업이 맞는지 확인하세요.",""))</f>
-        <v/>
-      </c>
+      <c r="A17" s="16" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
@@ -977,10 +963,7 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="16">
-        <f>IF(COUNTIF(C9:C13,"■")=0,"",IF(OR(E19="",E20="",E22=""),"⚠ 위험작업이 있는 날입니다 — 현장소장·안전관리자·관리감독자 입회자를 적으세요.",""))</f>
-        <v/>
-      </c>
+      <c r="A23" s="16" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -1076,655 +1059,18 @@
           <t>확인자 : 현장소장</t>
         </is>
       </c>
-      <c r="F31" s="29">
-        <f>IF(E19="","",E19)</f>
-        <v/>
-      </c>
+      <c r="F31" s="29" t="n"/>
       <c r="H31" s="28" t="inlineStr">
         <is>
           <t>(서명)</t>
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="30" t="inlineStr">
         <is>
           <t>□ 칸은 목록에서 ■ 를 고르세요. 하늘색 칸 = 자동(작업 요일 · 확인자 이름). 빨간 글자는 안내입니다(인쇄해도 나옵니다 — 비우려면 칸을 채우세요).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="A9:B13"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A18:B22"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E21:F21"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="C9 C10 C11 C12 C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"□,■"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="E1" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>붙임 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>일요일·공휴일작업 안전작업계획서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="4" customHeight="1"/>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>현 장 명</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>시 공 사</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>소 재 지</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>가나시 가나동 일원</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>전화번호</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>02-0000-0000</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>팩스번호</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>02-0000-0001</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>공사기간</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="8" t="n">
-        <v>46090</v>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>46568</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>공사금액</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>1843</v>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>백만원</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>위험작업</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>타워크레인 설치・조립・해체작업</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>고위험작업</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>건설용리프트 설치・조립・해체작업</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>고위험작업</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>굴착기・고소작업대・이동식크레인 사용작업</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>고위험작업</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>■</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>굴착작업(깊이 2미터 이상)</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="15" t="inlineStr"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>건물 등 해체작업</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="15" t="inlineStr"/>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="16">
-        <f>IF(COUNTIF(C9:C13,"■")=0,"","※ 체크한 위험작업 "&amp;COUNTIF(C9:C13,"■")&amp;"건"&amp;IF(((C9="■")+(C10="■")+(C11="■"))&gt;0," (고위험작업 "&amp;((C9="■")+(C10="■")+(C11="■"))&amp;"건)","")&amp;" — 작업내용·안전대책에 작업마다 대책을 적으세요.")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>기타작업</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>배수관 부설 준비(자재 정리)</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>작업업체명(공정)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>예시토건(주) (토공)</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>작업일시</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>46159</v>
-      </c>
-      <c r="G16" s="19">
-        <f>IF(N(F16)=0,"","("&amp;CHOOSE(WEEKDAY(F16),"일","월","화","수","목","금","토")&amp;")")</f>
-        <v/>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>08:00 ~ 17:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="16">
-        <f>IF(N(F16)=0,"",IF(WEEKDAY(F16,2)&lt;=5,"※ 작업일 "&amp;MONTH(F16)&amp;"/"&amp;DAY(F16)&amp;"("&amp;CHOOSE(WEEKDAY(F16),"일","월","화","수","목","금","토")&amp;")은 평일입니다 — 공휴일 작업이 맞는지 확인하세요.",""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>주말작업 입회
-관리자 명단</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>구    분</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>성    명</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="21" t="inlineStr">
-        <is>
-          <t>연 락 처</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>현장소장</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>010-0000-0001</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>안전관리자</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="20" t="inlineStr">
-        <is>
-          <t>010-0000-0002</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>협력사 현장소장</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="22" t="inlineStr">
-        <is>
-          <t>이영희</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>010-0000-0003</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>관리감독자</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>박민수</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>010-0000-0004</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="16">
-        <f>IF(COUNTIF(C9:C13,"■")=0,"",IF(OR(E19="",E20="",E22=""),"⚠ 위험작업이 있는 날입니다 — 현장소장·안전관리자·관리감독자 입회자를 적으세요.",""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>투입장비</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>굴착기 0.6㎥ 2대 · 덤프트럭 15t 3대 · 카고크레인 5t 1대</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>사고시
-비상대응체계</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>사고 발생 → 현장소장(홍길동) 보고 → 119 신고 · 가나병원 응급실(차량 10분) → 본사 안전팀 보고</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>작 업 내 용</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="21" t="inlineStr">
-        <is>
-          <t>안 전 대 책</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-    </row>
-    <row r="27" ht="130" customHeight="1">
-      <c r="A27" s="23" t="inlineStr">
-        <is>
-          <t>○ STA.0+260 ~ 0+340 배수로 터파기(깊이 2.5m)
-○ PC 암거 거치 6개
-○ 되메우기 L=40m</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>○ 굴착면 기울기 1:0.5 유지 · 작업 전 흙막이 상태 확인
-○ 굴착기 작업반경 출입 금지 · 신호수 1명 배치
-○ 암거 매달기 전 줄걸이 용구 점검
-○ 작업 전 TBM · 음주 여부 확인</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="8" customHeight="1"/>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="24" t="n">
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="25" t="inlineStr"/>
-      <c r="D30" s="26" t="inlineStr">
-        <is>
-          <t>작 성 자 :</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="H30" s="28" t="inlineStr">
-        <is>
-          <t>(서명)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="25" t="inlineStr"/>
-      <c r="D31" s="26" t="inlineStr">
-        <is>
-          <t>확인자 : 현장소장</t>
-        </is>
-      </c>
-      <c r="F31" s="29">
-        <f>IF(E19="","",E19)</f>
-        <v/>
-      </c>
-      <c r="H31" s="28" t="inlineStr">
-        <is>
-          <t>(서명)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="30" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사 · 회사 · 사람 · 번호).</t>
         </is>
       </c>
     </row>

--- a/web/public/forms/orig/o-hyuil-jageop.xlsx
+++ b/web/public/forms/orig/o-hyuil-jageop.xlsx
@@ -635,7 +635,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
